--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-11).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>R$ 1.591.760,33</t>
-  </si>
-  <si>
-    <t>R$ 8.512,09
-R$ 8.686,24</t>
-  </si>
-  <si>
-    <t>(4.3%)
-(2.8%)</t>
-  </si>
-  <si>
-    <t>91.8</t>
+182</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 1.640.630,11</t>
+  </si>
+  <si>
+    <t>R$ 8.500,67
+R$ 8.668,39</t>
+  </si>
+  <si>
+    <t>(4.6%)
+(3.2%)</t>
+  </si>
+  <si>
+    <t>91.7</t>
   </si>
   <si>
     <t>(7.8%)</t>
   </si>
   <si>
-    <t>36.4%</t>
-  </si>
-  <si>
-    <t>(8.4%)</t>
+    <t>46.4%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -947,34 +947,34 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>14.1%</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>20.6</t>
-  </si>
-  <si>
-    <t>64.5%</t>
-  </si>
-  <si>
-    <t>-R$ 48.167,60</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>14.2%</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>14.1</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>-R$ 48.373,80</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>15090.32</v>
+      </c>
+      <c r="P6" s="5">
+        <v>15090.32</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.028239533165983932</v>
+      </c>
+      <c r="R6" s="7">
+        <v>167</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.11333333333333329</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.3034879843502325</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0075034326641184555</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.021469663996522274</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0031527429504477041</v>
+      </c>
+      <c r="X6" s="8">
+        <v>23.588930597014926</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>7.836926347305389</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.0703007518796994</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>10.097911</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>17.021144029850745</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.93283582089552242</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>10252.17</v>
+      </c>
+      <c r="P24" s="5">
+        <v>10252.17</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.0088474414155905734</v>
+      </c>
+      <c r="R24" s="7">
+        <v>111</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.11904761904761907</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.053191470683767436</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.27796476258197045</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.020317796134867058</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0026171532465809676</v>
+      </c>
+      <c r="X24" s="8">
+        <v>32.481417241379312</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.54022988505747127</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.18390804597701149</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>6.0100305555555558</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.1563218390804604</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>22.321072413793104</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.42528735632183906</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-206.19999999999999</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5924,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7173.8800000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7173.8800000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.066525927687916431</v>
+      </c>
+      <c r="R36" s="7">
+        <v>117</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.69565217391304346</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.3745755156205568</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.015127127858285893</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.047493127847134324</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.010436472313448231</v>
+      </c>
+      <c r="X36" s="8">
+        <v>59.678333333333335</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.91111111111111109</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.62222222222222223</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>10.822968907563025</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>32.33425888888889</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>44.742776999999997</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>51.698888888888888</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.27777777777777779</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7845,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7881,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1111.8499999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1111.8499999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.066154613275032137</v>
+      </c>
+      <c r="R51" s="7">
+        <v>10</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.35325808337455594</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.012923056167648514</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.11403651571704818</v>
+      </c>
+      <c r="X51" s="8">
+        <v>26.966650000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.3200000000000003</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>11.275</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>15.958333</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>22.841650000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12600,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12639,7 +12781,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12673,25 +12815,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>9964.6599999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>9964.6599999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.2229272739608199</v>
+      </c>
+      <c r="R89" s="7">
+        <v>91</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.28346456692913391</v>
+      </c>
+      <c r="T89" s="6">
+        <v>17.291599041010933</v>
+      </c>
+      <c r="U89" s="6">
+        <v>16.931154229045447</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.026169482952755035</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.012387778408897042</v>
+      </c>
+      <c r="X89" s="8">
+        <v>31.469607843137254</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>6.7153699999999992</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>8.7770833333333336</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>22.97483725490196</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.41176470588235292</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15437,7 +15613,9 @@
       <c r="AB111" s="8">
         <v>1.2529749999999999</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.9771130000000001</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.756546428571427</v>
       </c>
@@ -15449,7 +15627,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15802,7 +15980,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16677,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16939,7 +17117,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17332,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18509,7 +18687,7 @@
         <v>-51.899999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18616,7 +18794,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20803,7 +20981,7 @@
         <v>-3561.4299999999998</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -20930,7 +21108,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21360,7 +21538,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21396,25 +21574,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>5276.8999999999996</v>
+      </c>
+      <c r="P158" s="5">
+        <v>5276.8999999999996</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.52614895565812403</v>
+      </c>
+      <c r="R158" s="7">
+        <v>47</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.5688073394495412</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.30553192215126307</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.012283992495594004</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.11234114726449242</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.072543159809736787</v>
+      </c>
+      <c r="X158" s="8">
+        <v>20.66060606060606</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>2.392156862745098</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.2151515151515149</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>5.5087489999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>12.659090909090908</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.87878787878787878</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22051,7 +22265,7 @@
         <v>-2176.6599999999999</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24121,7 +24335,9 @@
       <c r="AB179" s="8">
         <v>1.4542627906976744</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.2666659999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.200000000000001</v>
       </c>
@@ -28206,7 +28422,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
